--- a/报关资料模板（只有一个商品）.xlsx
+++ b/报关资料模板（只有一个商品）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowWidth="21600" windowHeight="9555" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="委托书" sheetId="5" r:id="rId1"/>
@@ -48,6 +48,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">     我单位现  </t>
     </r>
     <r>
@@ -456,6 +461,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>贸易国：</t>
     </r>
     <r>
@@ -558,6 +569,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="24"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>合</t>
     </r>
     <r>
@@ -565,7 +582,6 @@
         <b/>
         <sz val="24"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">       </t>
@@ -604,7 +620,6 @@
         <u/>
         <sz val="20"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t>CONTRACT</t>
@@ -612,6 +627,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">       </t>
     </r>
     <r>
@@ -626,7 +646,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">    </t>
@@ -645,6 +664,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">    </t>
     </r>
     <r>
@@ -659,7 +683,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">    </t>
@@ -678,6 +701,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">    </t>
     </r>
     <r>
@@ -691,6 +719,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">    </t>
     </r>
     <r>
@@ -705,7 +738,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">    </t>
@@ -722,7 +754,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -742,6 +773,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">    </t>
     </r>
     <r>
@@ -756,7 +792,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">     </t>
@@ -772,32 +807,20 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">  买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>方：</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">    Date:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  Buyers</t>
+      <t xml:space="preserve">  买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
     </r>
     <r>
       <rPr>
@@ -805,15 +828,20 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：</t>
-    </r>
-  </si>
-  <si>
-    <t>签约地点</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
+      <t>方：</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    Date:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">  Buyers</t>
     </r>
     <r>
       <rPr>
@@ -821,16 +849,20 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>地</t>
-    </r>
+      <t>：</t>
+    </r>
+  </si>
+  <si>
+    <t>签约地点</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
-      <t xml:space="preserve">   </t>
+      <t xml:space="preserve">  </t>
     </r>
     <r>
       <rPr>
@@ -838,22 +870,15 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>址：</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">  Signed at:</t>
-  </si>
-  <si>
-    <t>Address:</t>
-  </si>
-  <si>
-    <t>成交方式：
-Trade Term:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
+      <t>地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
     </r>
     <r>
       <rPr>
@@ -861,16 +886,27 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>电</t>
-    </r>
+      <t>址：</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  Signed at:</t>
+  </si>
+  <si>
+    <t>Address:</t>
+  </si>
+  <si>
+    <t>成交方式：
+Trade Term:</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
-      <t xml:space="preserve">   </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -878,20 +914,40 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>话</t>
+      <t>电</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">  </t>
     </r>
     <r>
@@ -906,7 +962,6 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -923,7 +978,6 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -940,6 +994,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(1)</t>
     </r>
     <r>
@@ -953,6 +1012,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">(2) </t>
     </r>
     <r>
@@ -967,7 +1031,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -983,6 +1046,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(3)</t>
     </r>
     <r>
@@ -997,7 +1065,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1013,6 +1080,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(4)</t>
     </r>
     <r>
@@ -1026,6 +1098,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve"> (5)   </t>
     </r>
     <r>
@@ -1040,7 +1117,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -1071,28 +1147,38 @@
   </si>
   <si>
     <r>
-      <t>数量及总值允许有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> 2 %</t>
-    </r>
-    <r>
       <rPr>
         <sz val="10"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>数量及总值允许有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> 2 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>的增减。</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">   </t>
     </r>
     <r>
@@ -1109,7 +1195,6 @@
         <b/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">      </t>
@@ -1138,6 +1223,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(7)</t>
     </r>
     <r>
@@ -1151,13 +1241,17 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">Packing and shipping Marks:  </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1165,6 +1259,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(8)</t>
     </r>
     <r>
@@ -1184,6 +1283,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(9)</t>
     </r>
     <r>
@@ -1198,7 +1302,6 @@
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">           </t>
@@ -1215,7 +1318,6 @@
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t>---</t>
@@ -1241,6 +1343,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t>(12)</t>
     </r>
     <r>
@@ -1257,6 +1364,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">    </t>
     </r>
     <r>
@@ -1271,7 +1383,6 @@
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -1287,6 +1398,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">    </t>
     </r>
     <r>
@@ -1301,7 +1417,6 @@
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -1320,6 +1435,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">  </t>
     </r>
     <r>
@@ -1327,7 +1447,6 @@
         <u/>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
         <charset val="0"/>
       </rPr>
       <t>THE SELLERS</t>
@@ -1387,37 +1506,45 @@
   PACKING LIST</t>
   </si>
   <si>
-    <r>
-      <t>日期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">
-Date</t>
-    </r>
     <r>
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>发票编号</t>
+      <t>日期</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发票编号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
         <charset val="0"/>
       </rPr>
       <t xml:space="preserve">
@@ -1426,6 +1553,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>客户</t>
     </r>
     <r>
@@ -1440,43 +1572,51 @@
   </si>
   <si>
     <r>
-      <t>合同号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">
-Contract No:</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-  </si>
-  <si>
-    <r>
-      <t>船名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">
-Shipped by</t>
-    </r>
-    <r>
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>合同号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+Contract No:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>船名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+Shipped by</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>：</t>
     </r>
   </si>
@@ -1485,6 +1625,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>付款条件</t>
     </r>
     <r>
@@ -1617,6 +1762,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>非互认国家（地区）AEO企业等其他情形，编码免于填报。</t>
     </r>
     <r>
@@ -1633,6 +1784,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>填报货物</t>
     </r>
     <r>
@@ -1674,6 +1830,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>填报进口货物在运抵我国关境前的</t>
     </r>
     <r>
@@ -1699,6 +1860,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>发生商业性交易的</t>
     </r>
     <r>
@@ -1753,6 +1919,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>经停港填报进口货物在运抵我国关境前的</t>
     </r>
     <r>
@@ -1770,6 +1941,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>指运港填报出口货物</t>
     </r>
     <r>
@@ -1840,6 +2016,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>填报由13位数字组成的商品编号。</t>
     </r>
     <r>
@@ -1871,6 +2053,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>分三行填报。</t>
     </r>
     <r>
@@ -1896,6 +2083,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>填报同一项号下进出口货物实际成交的商品单位价格。</t>
     </r>
     <r>
@@ -1913,6 +2105,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>填报同一项号下进出口货物实际成交的商品总价格。</t>
     </r>
     <r>
@@ -1948,6 +2145,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>境内货源地填报出口货物在</t>
     </r>
     <r>
@@ -1976,6 +2178,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>出口货物免予填报</t>
     </r>
     <r>
@@ -1992,6 +2200,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>出口货物免予填报</t>
     </r>
     <r>
@@ -2008,6 +2222,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>出口货物免予填报</t>
     </r>
     <r>
@@ -2096,7 +2316,6 @@
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -2113,19 +2332,16 @@
     <font>
       <sz val="20"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -2137,7 +2353,6 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -2167,27 +2382,23 @@
       <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -2394,23 +2605,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="24"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -2424,8 +2621,20 @@
       <u/>
       <sz val="20"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -5636,7 +5845,7 @@
       </c>
       <c r="H23" s="347">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="I23" s="347"/>
       <c r="J23" s="347"/>
@@ -5672,7 +5881,7 @@
       </c>
       <c r="C25" s="352">
         <f ca="1">报关单!L3</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="D25" s="353"/>
       <c r="E25" s="352"/>
@@ -5924,7 +6133,7 @@
       <c r="D45" s="385"/>
       <c r="E45" s="386">
         <f ca="1">TODAY()-1</f>
-        <v>46160</v>
+        <v>46166</v>
       </c>
       <c r="G45" s="365" t="s">
         <v>41</v>
@@ -5932,7 +6141,7 @@
       <c r="H45" s="387"/>
       <c r="I45" s="388">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="J45" s="389"/>
     </row>
@@ -6111,7 +6320,7 @@
       </c>
       <c r="L3" s="206">
         <f ca="1">委托书!I45</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="M3" s="200"/>
       <c r="N3" s="201"/>
@@ -10014,7 +10223,7 @@
       </c>
       <c r="G9" s="134">
         <f ca="1">报关单!L3</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="H9" s="134"/>
       <c r="I9" s="134"/>
@@ -10739,7 +10948,7 @@
       </c>
       <c r="C44" s="187">
         <f ca="1">TODAY()+30</f>
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="D44" s="187"/>
       <c r="E44" s="112" t="s">
@@ -11073,7 +11282,7 @@
       </c>
       <c r="G4" s="89">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="H4" s="90"/>
     </row>
@@ -11672,7 +11881,7 @@
       </c>
       <c r="G3" s="34">
         <f ca="1">报关单!L3</f>
-        <v>46161</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11">
